--- a/TextGame project/Assets/Resources/Story/8.xlsx
+++ b/TextGame project/Assets/Resources/Story/8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE160D84-1F23-4236-9B69-08D6A1A47963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB593728-3B4B-43DB-BCA6-C91487C8F324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -827,7 +827,7 @@
         <v>7</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>35</v>
@@ -855,7 +855,7 @@
         <v>7</v>
       </c>
       <c r="S3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T3" s="1">
         <v>-640.83010000000002</v>
@@ -878,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T4" s="1">
         <v>-640.83010000000002</v>
@@ -901,7 +901,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T5" s="1">
         <v>-640.83010000000002</v>
@@ -924,7 +924,7 @@
         <v>7</v>
       </c>
       <c r="S6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T6" s="1">
         <v>-640.83010000000002</v>
@@ -947,7 +947,7 @@
         <v>7</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T7" s="1">
         <v>-640.83010000000002</v>
@@ -970,7 +970,7 @@
         <v>7</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T8" s="1">
         <v>-640.83010000000002</v>
@@ -1002,7 +1002,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T9" s="1">
         <v>-640.83010000000002</v>
@@ -1025,7 +1025,7 @@
         <v>7</v>
       </c>
       <c r="S10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T10" s="1">
         <v>-640.83010000000002</v>
@@ -1048,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="S11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T11" s="1">
         <v>-640.83010000000002</v>
@@ -1071,7 +1071,7 @@
         <v>7</v>
       </c>
       <c r="S12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="1">
         <v>-640.83010000000002</v>

--- a/TextGame project/Assets/Resources/Story/8.xlsx
+++ b/TextGame project/Assets/Resources/Story/8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Text-Game\TextGame project\Assets\Resources\Story\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB593728-3B4B-43DB-BCA6-C91487C8F324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2AB1562-A138-4921-BBEA-AFBDFDAE13CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>Name</t>
   </si>
@@ -167,6 +167,14 @@
   </si>
   <si>
     <t>（带着哭腔）林深！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qianye2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -239,7 +247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,6 +267,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -917,8 +926,17 @@
       <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C6" t="s">
-        <v>23</v>
+      <c r="C6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="R6" s="4">
         <v>7</v>
@@ -1043,6 +1061,15 @@
       </c>
       <c r="C11" t="s">
         <v>23</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-640.83010000000002</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="R11" s="4">
         <v>7</v>
